--- a/记账.xlsx
+++ b/记账.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\信用卡\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\finjun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FE3E1D-6AC1-4D8B-9D3C-ACC05384ED77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC5A2B8-3B8B-49CA-B63E-81945868353C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="4560" windowWidth="28800" windowHeight="15460" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一期" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,13 @@
     <sheet name="第十期" sheetId="10" r:id="rId10"/>
     <sheet name="第十一期" sheetId="11" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">第二期!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">第六期!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">第三期!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">第四期!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">第一期!$A$2:$C$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -47,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="26">
   <si>
     <t>邮政银行</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -140,6 +147,18 @@
     <t>上期欠款</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>转33098.4*1.0057成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转35000*1.0057成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -187,9 +206,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -470,37 +490,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A2:E20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="3" max="3" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>20250428</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C1">
+      <c r="C2">
         <v>-27000</v>
       </c>
-      <c r="E1">
+      <c r="E2">
         <f>0.9945</f>
         <v>0.99450000000000005</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>20250429</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>-22929.53</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -508,19 +517,18 @@
         <v>20250429</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <f>19000*0.9945</f>
-        <v>18895.5</v>
+        <v>-22929.53</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>20250430</v>
+        <v>20250429</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <f>19000*0.9945</f>
@@ -529,25 +537,25 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>20250502</v>
+        <v>20250430</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>-30000</v>
+        <f>19000*0.9945</f>
+        <v>18895.5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>20250504</v>
+        <v>20250502</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="C6">
-        <f>15000*0.9945</f>
-        <v>14917.5</v>
+        <v>-30000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -558,8 +566,8 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <f>12000*0.9945</f>
-        <v>11934</v>
+        <f>15000*0.9945</f>
+        <v>14917.5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -570,43 +578,43 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>-30000</v>
+        <f>12000*0.9945</f>
+        <v>11934</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
+        <v>20250504</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
         <f>20250505</f>
         <v>20250505</v>
       </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9">
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10">
         <f>18000*0.9945</f>
         <v>17901</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>20250506</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>-20000</v>
-      </c>
-    </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>20250508</v>
+        <v>20250506</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="C11">
-        <f>19500*0.9945</f>
-        <v>19392.75</v>
+        <v>-20000</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -617,8 +625,8 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <f>11000*0.9945</f>
-        <v>10939.5</v>
+        <f>19500*0.9945</f>
+        <v>19392.75</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -626,11 +634,11 @@
         <v>20250508</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <f>7300*0.9945</f>
-        <v>7259.85</v>
+        <f>11000*0.9945</f>
+        <v>10939.5</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -638,11 +646,11 @@
         <v>20250508</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <f>3400*0.9945</f>
-        <v>3381.3</v>
+        <f>7300*0.9945</f>
+        <v>7259.85</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -650,34 +658,34 @@
         <v>20250508</v>
       </c>
       <c r="B15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>-34619.589999999997</v>
+        <f>3400*0.9945</f>
+        <v>3381.3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
+        <v>20250508</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>-34619.589999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>20250509</v>
       </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16">
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17">
         <f>19000*0.9945</f>
         <v>18895.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>20250510</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17">
-        <f>17400*0.9945</f>
-        <v>17304.3</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -685,15 +693,27 @@
         <v>20250510</v>
       </c>
       <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <f>17400*0.9945</f>
+        <v>17304.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>20250510</v>
+      </c>
+      <c r="B19" t="s">
         <v>3</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C19">
-        <f>SUM(C1:C18)</f>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C20">
+        <f>SUM(C2:C19)</f>
         <v>-5332.4199999999946</v>
       </c>
     </row>
@@ -904,13 +924,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E59C17-2726-4E5D-87FA-8C53A451D204}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>20260208</v>
       </c>
@@ -921,7 +941,7 @@
         <v>-80712.5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>20260208</v>
       </c>
@@ -932,7 +952,7 @@
         <v>-31650.61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>20260208</v>
       </c>
@@ -944,7 +964,7 @@
         <v>31326.75</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>20260212</v>
       </c>
@@ -955,7 +975,7 @@
         <v>-34999</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>20260212</v>
       </c>
@@ -967,7 +987,7 @@
         <v>34310.25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>20260212</v>
       </c>
@@ -975,10 +995,10 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>20260212</v>
       </c>
@@ -987,10 +1007,10 @@
       </c>
       <c r="C7">
         <f>SUM(C1:C6)</f>
-        <v>-81425.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-82025.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>20260212</v>
       </c>
@@ -999,7 +1019,82 @@
       </c>
       <c r="C8">
         <f>C7*1.0055</f>
-        <v>-81872.948105000003</v>
+        <v>-82476.248105000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>20260304</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <f>-35000*1.0057</f>
+        <v>-35199.5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>20260310</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <f>-33098.4*1.0057</f>
+        <v>-33287.060880000005</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>20260310</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>-300</v>
+      </c>
+      <c r="D11">
+        <v>68098.399999999994</v>
+      </c>
+      <c r="E11">
+        <f>D11-35000</f>
+        <v>33098.399999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>20260310</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(C8:C11)</f>
+        <v>-151262.80898500001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>20260310</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <f>C12*1.01</f>
+        <v>-152775.43707485002</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/记账.xlsx
+++ b/记账.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\finjun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC5A2B8-3B8B-49CA-B63E-81945868353C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C4159D-EFE4-4F11-8A8F-FE6720D89EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="26">
   <si>
     <t>邮政银行</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -924,7 +924,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E59C17-2726-4E5D-87FA-8C53A451D204}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1095,6 +1095,40 @@
       </c>
       <c r="D13" s="2">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>20260316</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>-24000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>20260316</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <f>23500*0.9945</f>
+        <v>23370.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>20260317</v>
+      </c>
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>-34500</v>
       </c>
     </row>
   </sheetData>

--- a/记账.xlsx
+++ b/记账.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\finjun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C4159D-EFE4-4F11-8A8F-FE6720D89EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E383F3-2095-4F4D-B928-8BF47574F6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一期" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,8 @@
     <sheet name="第九期" sheetId="9" r:id="rId9"/>
     <sheet name="第十期" sheetId="10" r:id="rId10"/>
     <sheet name="第十一期" sheetId="11" r:id="rId11"/>
+    <sheet name="第十二期" sheetId="12" r:id="rId12"/>
+    <sheet name="第十三期" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">第二期!$A$1:$G$23</definedName>
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="36">
   <si>
     <t>邮政银行</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,6 +159,46 @@
   </si>
   <si>
     <t>计息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还款5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手续费300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1%利息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>华夏邮政上期欠款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300手续费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月1%利息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（7月3日转支付宝6000，微信有转账过-3500）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手续费</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -924,13 +966,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E59C17-2726-4E5D-87FA-8C53A451D204}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>20260208</v>
       </c>
@@ -941,7 +983,7 @@
         <v>-80712.5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>20260208</v>
       </c>
@@ -952,7 +994,7 @@
         <v>-31650.61</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>20260208</v>
       </c>
@@ -964,7 +1006,7 @@
         <v>31326.75</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>20260212</v>
       </c>
@@ -975,7 +1017,7 @@
         <v>-34999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>20260212</v>
       </c>
@@ -987,7 +1029,7 @@
         <v>34310.25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>20260212</v>
       </c>
@@ -998,7 +1040,7 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>20260212</v>
       </c>
@@ -1010,7 +1052,7 @@
         <v>-82025.11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>20260212</v>
       </c>
@@ -1022,7 +1064,7 @@
         <v>-82476.248105000006</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>20260304</v>
       </c>
@@ -1037,7 +1079,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>20260310</v>
       </c>
@@ -1052,7 +1094,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>20260310</v>
       </c>
@@ -1070,7 +1112,7 @@
         <v>33098.399999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>20260310</v>
       </c>
@@ -1082,7 +1124,7 @@
         <v>-151262.80898500001</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>20260310</v>
       </c>
@@ -1097,7 +1139,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>20260316</v>
       </c>
@@ -1107,8 +1149,15 @@
       <c r="C14">
         <v>-24000</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14">
+        <v>32050.61</v>
+      </c>
+      <c r="F14">
+        <f>E14+C14</f>
+        <v>8050.6100000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>20260316</v>
       </c>
@@ -1120,7 +1169,7 @@
         <v>23370.75</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>20260317</v>
       </c>
@@ -1129,6 +1178,532 @@
       </c>
       <c r="C16">
         <v>-34500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>20260317</v>
+      </c>
+      <c r="B17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <f>34000*0.9945</f>
+        <v>33813</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>20260323</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>-8050.61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>20260323</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <f>8000*0.9945</f>
+        <v>7956</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>20230323</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <f>SUM(C14:C20)</f>
+        <v>-1710.8600000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{952344AE-7951-4FC6-A5A1-EC2CABB8065A}">
+  <dimension ref="A4:F40"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>20260410</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4">
+        <v>-152775</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>20260410</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <f>C4+5000</f>
+        <v>-147775</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>20260410</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <f>C5-300</f>
+        <v>-148075</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>20260410</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <f>C6*1.01</f>
+        <v>-149555.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <f>POWER(1.01,12)</f>
+        <v>1.1268250301319698</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>20260423</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11">
+        <v>-1710.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>20260422</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>-34499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>20260423</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>-32050.61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>20260423</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>20260423</v>
+      </c>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f>34480*0.9943</f>
+        <v>34283.464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>20260427</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <f>32000*0.9943</f>
+        <v>31817.599999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <f>SUM(C11:C16)</f>
+        <v>-2459.4060000000027</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>20260430</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22">
+        <v>-149556</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>20260430</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>20260430</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <f>C22+C23</f>
+        <v>-144556</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25">
+        <f>C24-300</f>
+        <v>-144856</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26">
+        <f>C25*1.01</f>
+        <v>-146304.56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>20260519</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28">
+        <v>-2459.41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>20260519</v>
+      </c>
+      <c r="B29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>-34480</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>20260520</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <f>34400*0.9945</f>
+        <v>34210.800000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>20260521</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>-32550.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>20260526</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>32321.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>20260526</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33">
+        <v>-300</v>
+      </c>
+      <c r="E33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C34">
+        <f>SUM(C28:C33)</f>
+        <v>-3258.1100000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>20260530</v>
+      </c>
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36">
+        <v>-146305</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>20260530</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>20260530</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38">
+        <f>SUM(C36:C37)</f>
+        <v>-141305</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39">
+        <f>-300+C38</f>
+        <v>-141605</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40">
+        <f>C39*1.01</f>
+        <v>-143021.04999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{216D9210-3DDA-47EC-98B6-2A056086F26C}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>20260614</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1">
+        <v>-3258.11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>20260614</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>-34400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>20260614</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>34300*0.9945</f>
+        <v>34111.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>20260616</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>-32500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>20260617</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <f>32400*0.9945</f>
+        <v>32221.800000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>20206617</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>20260617</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <f>SUM(C1:C6)</f>
+        <v>-4124.9599999999991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>20260630</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>-143021</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>20260630</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>5000</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>20260630</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <f>SUM(C9:C11)</f>
+        <v>-138321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13">
+        <f>C12*1.01</f>
+        <v>-139704.21</v>
       </c>
     </row>
   </sheetData>
